--- a/docs/Recipe-import-task/anomaly-CBBCC-R1TEB.xlsx
+++ b/docs/Recipe-import-task/anomaly-CBBCC-R1TEB.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -812,6 +812,117 @@
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Used VEGCHI-11. Name match, no (FRESH) flag on the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Master file</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OC005</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Col X Case Name GMB2 323 x 210 x 195 matches OC005 / old PKCON001-19.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GMB2 323 X 210 X 195</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OC005 already on FG recipe L2 qty 1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Left recipe. Set packaging.box_id=OC005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Master file</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L780-03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Col AA=Sleeves Col AV=L780-03 still not in catalogue. No Booths Bang Bang sleeve.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L780-03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Not in catalogue</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Still omitted. Please add L780-03 then put qty 1 on CBBCC-R1TEB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Master file</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CBBCC-R1TEB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Filled inner barcode AF. Depot BF=8. Did not overwrite shelf_life_days=14 (AL=18 BE=10 clash).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AF 5028440673245; AL 18; BE 10; BF 8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>barcode set; depot=8; shelf_life_days left 14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Filled blanks only.</t>
         </is>
       </c>
     </row>
